--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CO$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO1"/>
+  <dimension ref="A1:CP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,6 +979,7 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="17" customWidth="1" min="94" max="94"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1447,9 +1448,14 @@
           <t>schedule_missingness</t>
         </is>
       </c>
+      <c r="CP1" s="23" t="inlineStr">
+        <is>
+          <t>trade_candidate</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CO1"/>
+  <autoFilter ref="A1:CP1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CP$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CQ$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -883,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CP1"/>
+  <dimension ref="A1:CQ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -979,7 +979,8 @@
     <col width="18" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
     <col width="22" customWidth="1" min="93" max="93"/>
-    <col width="17" customWidth="1" min="94" max="94"/>
+    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="17" customWidth="1" min="95" max="95"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1450,12 +1451,17 @@
       </c>
       <c r="CP1" s="23" t="inlineStr">
         <is>
+          <t>market_residual_probability</t>
+        </is>
+      </c>
+      <c r="CQ1" s="23" t="inlineStr">
+        <is>
           <t>trade_candidate</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CP1"/>
+  <autoFilter ref="A1:CQ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
 </worksheet>

--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -12,7 +12,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CQ$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,111 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR3" headerRowCount="1">
+  <autoFilter ref="A1:CR3"/>
+  <tableColumns count="96">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="rest_disparity"/>
+    <tableColumn id="92" name="back_to_back_gap"/>
+    <tableColumn id="93" name="games_last_7_gap"/>
+    <tableColumn id="94" name="schedule_missingness"/>
+    <tableColumn id="95" name="market_residual_probability"/>
+    <tableColumn id="96" name="trade_candidate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +755,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +795,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +835,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$3)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +902,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +918,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +933,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +949,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +964,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +980,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CQ1"/>
+  <dimension ref="A1:CR3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -975,12 +1105,13 @@
     <col width="22" customWidth="1" min="87" max="87"/>
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
-    <col width="16" customWidth="1" min="90" max="90"/>
-    <col width="18" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="90" max="90"/>
+    <col width="16" customWidth="1" min="91" max="91"/>
     <col width="18" customWidth="1" min="92" max="92"/>
-    <col width="22" customWidth="1" min="93" max="93"/>
+    <col width="18" customWidth="1" min="93" max="93"/>
     <col width="22" customWidth="1" min="94" max="94"/>
-    <col width="17" customWidth="1" min="95" max="95"/>
+    <col width="22" customWidth="1" min="95" max="95"/>
+    <col width="17" customWidth="1" min="96" max="96"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1431,38 +1562,581 @@
       </c>
       <c r="CL1" s="23" t="inlineStr">
         <is>
+          <t>bullpen_weakness_gap</t>
+        </is>
+      </c>
+      <c r="CM1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CM1" s="23" t="inlineStr">
+      <c r="CN1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>1440d05212434473</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:23.496239Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T12:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>68312</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>CAG by VARREL</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.573086</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.202716</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="n"/>
+      <c r="W2" s="26" t="n"/>
+      <c r="X2" s="26" t="n"/>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n"/>
+      <c r="AA2" s="28" t="n"/>
+      <c r="AB2" s="28" t="n"/>
+      <c r="AC2" s="30" t="n"/>
+      <c r="AD2" s="24" t="n"/>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-r6-cbv-fnc-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Fnatic</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>CAG by VARREL</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>CAG by VARREL</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>CAG by VARREL</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.359164Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>170</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n"/>
+      <c r="BR2" s="28" t="n"/>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>993f4d87bb894e75</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:23.496239Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T13:20:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>68396</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>TYLOO</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>Chiefs Esports Club</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.68109</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.021226</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>31</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-r6-chf-tyloo-2026-08-04).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>TYLOO</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>TYLOO</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>TYLOO</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>Chiefs Esports Club</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>Chiefs Esports Club</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>Chiefs Esports Club</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v5</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-04T08:56:22.971695Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-194</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.515464</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.659864</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CQ1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -12,6 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CS$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -20,11 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="0.0###"/>
-    <numFmt numFmtId="165" formatCode="0.000000"/>
-    <numFmt numFmtId="166" formatCode="0.0000"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -38,11 +37,6 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -73,6 +67,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -136,61 +135,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -198,30 +197,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -297,111 +272,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CR3" headerRowCount="1">
-  <autoFilter ref="A1:CR3"/>
-  <tableColumns count="96">
-    <tableColumn id="1" name="pick_id"/>
-    <tableColumn id="2" name="created_at_utc"/>
-    <tableColumn id="3" name="event_start_utc"/>
-    <tableColumn id="4" name="event_id"/>
-    <tableColumn id="5" name="league"/>
-    <tableColumn id="6" name="away_team"/>
-    <tableColumn id="7" name="home_team"/>
-    <tableColumn id="8" name="market_type"/>
-    <tableColumn id="9" name="selection"/>
-    <tableColumn id="10" name="line"/>
-    <tableColumn id="11" name="sportsbook"/>
-    <tableColumn id="12" name="american_odds"/>
-    <tableColumn id="13" name="decimal_odds"/>
-    <tableColumn id="14" name="market_implied_probability"/>
-    <tableColumn id="15" name="model_probability"/>
-    <tableColumn id="16" name="model_uncertainty"/>
-    <tableColumn id="17" name="edge"/>
-    <tableColumn id="18" name="confidence_score"/>
-    <tableColumn id="19" name="units"/>
-    <tableColumn id="20" name="model_version"/>
-    <tableColumn id="21" name="status"/>
-    <tableColumn id="22" name="result"/>
-    <tableColumn id="23" name="away_score"/>
-    <tableColumn id="24" name="home_score"/>
-    <tableColumn id="25" name="closing_line"/>
-    <tableColumn id="26" name="closing_american_odds"/>
-    <tableColumn id="27" name="closing_implied_probability"/>
-    <tableColumn id="28" name="probability_clv"/>
-    <tableColumn id="29" name="pnl_units"/>
-    <tableColumn id="30" name="settled_at_utc"/>
-    <tableColumn id="31" name="rationale"/>
-    <tableColumn id="32" name="risks"/>
-    <tableColumn id="33" name="review_status"/>
-    <tableColumn id="34" name="loss_classification"/>
-    <tableColumn id="35" name="loss_cause"/>
-    <tableColumn id="36" name="corrective_action"/>
-    <tableColumn id="37" name="call_type"/>
-    <tableColumn id="38" name="ledger_schema_version"/>
-    <tableColumn id="39" name="record_type"/>
-    <tableColumn id="40" name="decision"/>
-    <tableColumn id="41" name="reason_code"/>
-    <tableColumn id="42" name="canonical_away_team_id"/>
-    <tableColumn id="43" name="canonical_away_team_name"/>
-    <tableColumn id="44" name="original_away_team"/>
-    <tableColumn id="45" name="canonical_home_team_id"/>
-    <tableColumn id="46" name="canonical_home_team_name"/>
-    <tableColumn id="47" name="original_home_team"/>
-    <tableColumn id="48" name="banned_team_id"/>
-    <tableColumn id="49" name="banned_team_name"/>
-    <tableColumn id="50" name="model_origin"/>
-    <tableColumn id="51" name="baseline_identifier"/>
-    <tableColumn id="52" name="model_state_at_decision"/>
-    <tableColumn id="53" name="model_artifact_hash"/>
-    <tableColumn id="54" name="calibration_method"/>
-    <tableColumn id="55" name="calibration_version"/>
-    <tableColumn id="56" name="calibration_artifact_hash"/>
-    <tableColumn id="57" name="feature_schema_version"/>
-    <tableColumn id="58" name="entity_map_version"/>
-    <tableColumn id="59" name="code_revision"/>
-    <tableColumn id="60" name="observed_at_utc"/>
-    <tableColumn id="61" name="correlation_tags"/>
-    <tableColumn id="62" name="decision_line"/>
-    <tableColumn id="63" name="decision_american_odds"/>
-    <tableColumn id="64" name="decision_decimal_odds"/>
-    <tableColumn id="65" name="decision_raw_implied_probability"/>
-    <tableColumn id="66" name="decision_no_vig_probability"/>
-    <tableColumn id="67" name="decision_consensus_probability"/>
-    <tableColumn id="68" name="decision_consensus_line"/>
-    <tableColumn id="69" name="closing_decimal_odds"/>
-    <tableColumn id="70" name="closing_raw_implied_probability"/>
-    <tableColumn id="71" name="closing_no_vig_probability"/>
-    <tableColumn id="72" name="closing_consensus_probability"/>
-    <tableColumn id="73" name="closing_consensus_line"/>
-    <tableColumn id="74" name="legacy_units"/>
-    <tableColumn id="75" name="void_reason"/>
-    <tableColumn id="76" name="research_score_units"/>
-    <tableColumn id="77" name="research_pnl_units"/>
-    <tableColumn id="78" name="research_scored_at_utc"/>
-    <tableColumn id="79" name="research_scoring_note"/>
-    <tableColumn id="80" name="migrated_from_version"/>
-    <tableColumn id="81" name="elo_probability"/>
-    <tableColumn id="82" name="trend_gap"/>
-    <tableColumn id="83" name="park_factor"/>
-    <tableColumn id="84" name="weather_factor"/>
-    <tableColumn id="85" name="pitcher_era_gap"/>
-    <tableColumn id="86" name="probable_starter_era_gap"/>
-    <tableColumn id="87" name="unavailable_features"/>
-    <tableColumn id="88" name="defensive_trend_gap"/>
-    <tableColumn id="89" name="neutral_elo_rating_difference"/>
-    <tableColumn id="90" name="bullpen_weakness_gap"/>
-    <tableColumn id="91" name="rest_disparity"/>
-    <tableColumn id="92" name="back_to_back_gap"/>
-    <tableColumn id="93" name="games_last_7_gap"/>
-    <tableColumn id="94" name="schedule_missingness"/>
-    <tableColumn id="95" name="market_residual_probability"/>
-    <tableColumn id="96" name="trade_candidate"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -755,19 +625,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$3)</f>
+        <f>COUNTA('Picks'!$A$2:$A$2)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -795,19 +665,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
         <v/>
       </c>
     </row>
@@ -835,19 +705,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$3)</f>
+        <f>SUM('Picks'!$BY$2:$BY$2)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -902,15 +772,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -918,11 +788,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -933,15 +803,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -949,11 +819,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -964,15 +834,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -980,11 +850,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1013,7 +883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CR3"/>
+  <dimension ref="A1:CS1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1106,12 +976,13 @@
     <col width="21" customWidth="1" min="88" max="88"/>
     <col width="22" customWidth="1" min="89" max="89"/>
     <col width="22" customWidth="1" min="90" max="90"/>
-    <col width="16" customWidth="1" min="91" max="91"/>
-    <col width="18" customWidth="1" min="92" max="92"/>
+    <col width="17" customWidth="1" min="91" max="91"/>
+    <col width="16" customWidth="1" min="92" max="92"/>
     <col width="18" customWidth="1" min="93" max="93"/>
-    <col width="22" customWidth="1" min="94" max="94"/>
+    <col width="18" customWidth="1" min="94" max="94"/>
     <col width="22" customWidth="1" min="95" max="95"/>
-    <col width="17" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="96" max="96"/>
+    <col width="17" customWidth="1" min="97" max="97"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1567,576 +1438,43 @@
       </c>
       <c r="CM1" s="23" t="inlineStr">
         <is>
+          <t>starter_era_gap</t>
+        </is>
+      </c>
+      <c r="CN1" s="23" t="inlineStr">
+        <is>
           <t>rest_disparity</t>
         </is>
       </c>
-      <c r="CN1" s="23" t="inlineStr">
+      <c r="CO1" s="23" t="inlineStr">
         <is>
           <t>back_to_back_gap</t>
         </is>
       </c>
-      <c r="CO1" s="23" t="inlineStr">
+      <c r="CP1" s="23" t="inlineStr">
         <is>
           <t>games_last_7_gap</t>
         </is>
       </c>
-      <c r="CP1" s="23" t="inlineStr">
+      <c r="CQ1" s="23" t="inlineStr">
         <is>
           <t>schedule_missingness</t>
         </is>
       </c>
-      <c r="CQ1" s="23" t="inlineStr">
+      <c r="CR1" s="23" t="inlineStr">
         <is>
           <t>market_residual_probability</t>
         </is>
       </c>
-      <c r="CR1" s="23" t="inlineStr">
+      <c r="CS1" s="23" t="inlineStr">
         <is>
           <t>trade_candidate</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="36" customHeight="1">
-      <c r="A2" s="24" t="inlineStr">
-        <is>
-          <t>1440d05212434473</t>
-        </is>
-      </c>
-      <c r="B2" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:23.496239Z</t>
-        </is>
-      </c>
-      <c r="C2" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T12:00:00Z</t>
-        </is>
-      </c>
-      <c r="D2" s="24" t="inlineStr">
-        <is>
-          <t>68312</t>
-        </is>
-      </c>
-      <c r="E2" s="24" t="inlineStr">
-        <is>
-          <t>RAINBOW_SIX</t>
-        </is>
-      </c>
-      <c r="F2" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="G2" s="24" t="inlineStr">
-        <is>
-          <t>CAG by VARREL</t>
-        </is>
-      </c>
-      <c r="H2" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I2" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J2" s="25" t="n"/>
-      <c r="K2" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L2" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="M2" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="N2" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="O2" s="28" t="n">
-        <v>0.573086</v>
-      </c>
-      <c r="P2" s="28" t="n"/>
-      <c r="Q2" s="28" t="n">
-        <v>0.202716</v>
-      </c>
-      <c r="R2" s="26" t="n">
-        <v>100</v>
-      </c>
-      <c r="S2" s="29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="T2" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U2" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V2" s="24" t="n"/>
-      <c r="W2" s="26" t="n"/>
-      <c r="X2" s="26" t="n"/>
-      <c r="Y2" s="25" t="n"/>
-      <c r="Z2" s="26" t="n"/>
-      <c r="AA2" s="28" t="n"/>
-      <c r="AB2" s="28" t="n"/>
-      <c r="AC2" s="30" t="n"/>
-      <c r="AD2" s="24" t="n"/>
-      <c r="AE2" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.3700 (market_slug=aec-r6-cbv-fnc-2026-08-04).</t>
-        </is>
-      </c>
-      <c r="AF2" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG2" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH2" s="24" t="n"/>
-      <c r="AI2" s="31" t="n"/>
-      <c r="AJ2" s="31" t="n"/>
-      <c r="AK2" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL2" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM2" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN2" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO2" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP2" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AQ2" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AR2" s="24" t="inlineStr">
-        <is>
-          <t>Fnatic</t>
-        </is>
-      </c>
-      <c r="AS2" s="24" t="inlineStr">
-        <is>
-          <t>CAG by VARREL</t>
-        </is>
-      </c>
-      <c r="AT2" s="24" t="inlineStr">
-        <is>
-          <t>CAG by VARREL</t>
-        </is>
-      </c>
-      <c r="AU2" s="24" t="inlineStr">
-        <is>
-          <t>CAG by VARREL</t>
-        </is>
-      </c>
-      <c r="AV2" s="24" t="n"/>
-      <c r="AW2" s="24" t="n"/>
-      <c r="AX2" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY2" s="24" t="n"/>
-      <c r="AZ2" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA2" s="24" t="inlineStr">
-        <is>
-          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
-        </is>
-      </c>
-      <c r="BB2" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC2" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD2" s="24" t="inlineStr">
-        <is>
-          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
-        </is>
-      </c>
-      <c r="BE2" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF2" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG2" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH2" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:22.359164Z</t>
-        </is>
-      </c>
-      <c r="BI2" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ2" s="25" t="n"/>
-      <c r="BK2" s="26" t="n">
-        <v>170</v>
-      </c>
-      <c r="BL2" s="27" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BM2" s="28" t="n">
-        <v>0.37037</v>
-      </c>
-      <c r="BN2" s="28" t="n"/>
-      <c r="BO2" s="28" t="n"/>
-      <c r="BP2" s="25" t="n"/>
-      <c r="BQ2" s="27" t="n"/>
-      <c r="BR2" s="28" t="n"/>
-      <c r="BS2" s="28" t="n"/>
-      <c r="BT2" s="28" t="n"/>
-      <c r="BU2" s="25" t="n"/>
-      <c r="BV2" s="29" t="n"/>
-      <c r="BW2" s="24" t="n"/>
-      <c r="BX2" s="30" t="n"/>
-      <c r="BY2" s="27" t="n"/>
-      <c r="BZ2" s="24" t="n"/>
-      <c r="CA2" s="31" t="n"/>
-      <c r="CB2" s="24" t="n"/>
-      <c r="CC2" s="24" t="n"/>
-      <c r="CD2" s="24" t="n"/>
-      <c r="CE2" s="24" t="n"/>
-      <c r="CF2" s="24" t="n"/>
-      <c r="CG2" s="24" t="n"/>
-      <c r="CH2" s="24" t="n"/>
-      <c r="CI2" s="24" t="n"/>
-      <c r="CJ2" s="24" t="n"/>
-      <c r="CK2" s="24" t="n"/>
-      <c r="CL2" s="24" t="n"/>
-      <c r="CM2" s="24" t="n"/>
-      <c r="CN2" s="24" t="n"/>
-      <c r="CO2" s="24" t="n"/>
-      <c r="CP2" s="24" t="n"/>
-      <c r="CQ2" s="24" t="n"/>
-      <c r="CR2" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="36" customHeight="1">
-      <c r="A3" s="24" t="inlineStr">
-        <is>
-          <t>993f4d87bb894e75</t>
-        </is>
-      </c>
-      <c r="B3" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:23.496239Z</t>
-        </is>
-      </c>
-      <c r="C3" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T13:20:00Z</t>
-        </is>
-      </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>68396</t>
-        </is>
-      </c>
-      <c r="E3" s="24" t="inlineStr">
-        <is>
-          <t>RAINBOW_SIX</t>
-        </is>
-      </c>
-      <c r="F3" s="24" t="inlineStr">
-        <is>
-          <t>TYLOO</t>
-        </is>
-      </c>
-      <c r="G3" s="24" t="inlineStr">
-        <is>
-          <t>Chiefs Esports Club</t>
-        </is>
-      </c>
-      <c r="H3" s="24" t="inlineStr">
-        <is>
-          <t>moneyline</t>
-        </is>
-      </c>
-      <c r="I3" s="24" t="inlineStr">
-        <is>
-          <t>home</t>
-        </is>
-      </c>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>polymarket_us</t>
-        </is>
-      </c>
-      <c r="L3" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="M3" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="N3" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="O3" s="28" t="n">
-        <v>0.68109</v>
-      </c>
-      <c r="P3" s="28" t="n"/>
-      <c r="Q3" s="28" t="n">
-        <v>0.021226</v>
-      </c>
-      <c r="R3" s="26" t="n">
-        <v>31</v>
-      </c>
-      <c r="S3" s="29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T3" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="U3" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
-      <c r="AE3" s="31" t="inlineStr">
-        <is>
-          <t>Neutral Elo baseline; executable ask 0.6600 (market_slug=aec-r6-chf-tyloo-2026-08-04).</t>
-        </is>
-      </c>
-      <c r="AF3" s="31" t="inlineStr">
-        <is>
-          <t>Config-promoted esports baseline; gates enforced at log time.</t>
-        </is>
-      </c>
-      <c r="AG3" s="24" t="inlineStr">
-        <is>
-          <t>not_applicable</t>
-        </is>
-      </c>
-      <c r="AH3" s="24" t="n"/>
-      <c r="AI3" s="31" t="n"/>
-      <c r="AJ3" s="31" t="n"/>
-      <c r="AK3" s="24" t="inlineStr">
-        <is>
-          <t>model_qualified</t>
-        </is>
-      </c>
-      <c r="AL3" s="26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AM3" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
-        </is>
-      </c>
-      <c r="AN3" s="24" t="inlineStr">
-        <is>
-          <t>CALL</t>
-        </is>
-      </c>
-      <c r="AO3" s="24" t="inlineStr">
-        <is>
-          <t>QUALIFIED</t>
-        </is>
-      </c>
-      <c r="AP3" s="24" t="inlineStr">
-        <is>
-          <t>TYLOO</t>
-        </is>
-      </c>
-      <c r="AQ3" s="24" t="inlineStr">
-        <is>
-          <t>TYLOO</t>
-        </is>
-      </c>
-      <c r="AR3" s="24" t="inlineStr">
-        <is>
-          <t>TYLOO</t>
-        </is>
-      </c>
-      <c r="AS3" s="24" t="inlineStr">
-        <is>
-          <t>Chiefs Esports Club</t>
-        </is>
-      </c>
-      <c r="AT3" s="24" t="inlineStr">
-        <is>
-          <t>Chiefs Esports Club</t>
-        </is>
-      </c>
-      <c r="AU3" s="24" t="inlineStr">
-        <is>
-          <t>Chiefs Esports Club</t>
-        </is>
-      </c>
-      <c r="AV3" s="24" t="n"/>
-      <c r="AW3" s="24" t="n"/>
-      <c r="AX3" s="24" t="inlineStr">
-        <is>
-          <t>statistical_model</t>
-        </is>
-      </c>
-      <c r="AY3" s="24" t="n"/>
-      <c r="AZ3" s="24" t="inlineStr">
-        <is>
-          <t>research</t>
-        </is>
-      </c>
-      <c r="BA3" s="24" t="inlineStr">
-        <is>
-          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
-        </is>
-      </c>
-      <c r="BB3" s="24" t="inlineStr">
-        <is>
-          <t>neutral_elo</t>
-        </is>
-      </c>
-      <c r="BC3" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BD3" s="24" t="inlineStr">
-        <is>
-          <t>312d289ff4fd9979bd0eeffb3fed32cf6083d1d4cc9fc38fe0d12286eee9b23e</t>
-        </is>
-      </c>
-      <c r="BE3" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BF3" s="24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="BG3" s="24" t="inlineStr">
-        <is>
-          <t>rainbow_six-tiered-elo-v5</t>
-        </is>
-      </c>
-      <c r="BH3" s="24" t="inlineStr">
-        <is>
-          <t>2026-08-04T08:56:22.971695Z</t>
-        </is>
-      </c>
-      <c r="BI3" s="24" t="inlineStr">
-        <is>
-          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
-        </is>
-      </c>
-      <c r="BJ3" s="25" t="n"/>
-      <c r="BK3" s="26" t="n">
-        <v>-194</v>
-      </c>
-      <c r="BL3" s="27" t="n">
-        <v>1.515464</v>
-      </c>
-      <c r="BM3" s="28" t="n">
-        <v>0.659864</v>
-      </c>
-      <c r="BN3" s="28" t="n"/>
-      <c r="BO3" s="28" t="n"/>
-      <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
-      <c r="BS3" s="28" t="n"/>
-      <c r="BT3" s="28" t="n"/>
-      <c r="BU3" s="25" t="n"/>
-      <c r="BV3" s="29" t="n"/>
-      <c r="BW3" s="24" t="n"/>
-      <c r="BX3" s="30" t="n"/>
-      <c r="BY3" s="27" t="n"/>
-      <c r="BZ3" s="24" t="n"/>
-      <c r="CA3" s="31" t="n"/>
-      <c r="CB3" s="24" t="n"/>
-      <c r="CC3" s="24" t="n"/>
-      <c r="CD3" s="24" t="n"/>
-      <c r="CE3" s="24" t="n"/>
-      <c r="CF3" s="24" t="n"/>
-      <c r="CG3" s="24" t="n"/>
-      <c r="CH3" s="24" t="n"/>
-      <c r="CI3" s="24" t="n"/>
-      <c r="CJ3" s="24" t="n"/>
-      <c r="CK3" s="24" t="n"/>
-      <c r="CL3" s="24" t="n"/>
-      <c r="CM3" s="24" t="n"/>
-      <c r="CN3" s="24" t="n"/>
-      <c r="CO3" s="24" t="n"/>
-      <c r="CP3" s="24" t="n"/>
-      <c r="CQ3" s="24" t="n"/>
-      <c r="CR3" s="24" t="inlineStr">
-        <is>
-          <t>True</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:CS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -1,18 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Picks" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Picks" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Summary'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Picks'!$A$1:$CS$1</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Picks'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
@@ -21,9 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="0.0###"/>
+    <numFmt numFmtId="165" formatCode="0.000000"/>
+    <numFmt numFmtId="166" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -37,6 +38,11 @@
       <name val="Aptos"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="001F2937"/>
       <sz val="10"/>
     </font>
     <font>
@@ -67,11 +73,6 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="001F2937"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -135,61 +136,61 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="7" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,6 +198,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -272,6 +297,112 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:CS3" headerRowCount="1">
+  <autoFilter ref="A1:CS3"/>
+  <tableColumns count="97">
+    <tableColumn id="1" name="pick_id"/>
+    <tableColumn id="2" name="created_at_utc"/>
+    <tableColumn id="3" name="event_start_utc"/>
+    <tableColumn id="4" name="event_id"/>
+    <tableColumn id="5" name="league"/>
+    <tableColumn id="6" name="away_team"/>
+    <tableColumn id="7" name="home_team"/>
+    <tableColumn id="8" name="market_type"/>
+    <tableColumn id="9" name="selection"/>
+    <tableColumn id="10" name="line"/>
+    <tableColumn id="11" name="sportsbook"/>
+    <tableColumn id="12" name="american_odds"/>
+    <tableColumn id="13" name="decimal_odds"/>
+    <tableColumn id="14" name="market_implied_probability"/>
+    <tableColumn id="15" name="model_probability"/>
+    <tableColumn id="16" name="model_uncertainty"/>
+    <tableColumn id="17" name="edge"/>
+    <tableColumn id="18" name="confidence_score"/>
+    <tableColumn id="19" name="units"/>
+    <tableColumn id="20" name="model_version"/>
+    <tableColumn id="21" name="status"/>
+    <tableColumn id="22" name="result"/>
+    <tableColumn id="23" name="away_score"/>
+    <tableColumn id="24" name="home_score"/>
+    <tableColumn id="25" name="closing_line"/>
+    <tableColumn id="26" name="closing_american_odds"/>
+    <tableColumn id="27" name="closing_implied_probability"/>
+    <tableColumn id="28" name="probability_clv"/>
+    <tableColumn id="29" name="pnl_units"/>
+    <tableColumn id="30" name="settled_at_utc"/>
+    <tableColumn id="31" name="rationale"/>
+    <tableColumn id="32" name="risks"/>
+    <tableColumn id="33" name="review_status"/>
+    <tableColumn id="34" name="loss_classification"/>
+    <tableColumn id="35" name="loss_cause"/>
+    <tableColumn id="36" name="corrective_action"/>
+    <tableColumn id="37" name="call_type"/>
+    <tableColumn id="38" name="ledger_schema_version"/>
+    <tableColumn id="39" name="record_type"/>
+    <tableColumn id="40" name="decision"/>
+    <tableColumn id="41" name="reason_code"/>
+    <tableColumn id="42" name="canonical_away_team_id"/>
+    <tableColumn id="43" name="canonical_away_team_name"/>
+    <tableColumn id="44" name="original_away_team"/>
+    <tableColumn id="45" name="canonical_home_team_id"/>
+    <tableColumn id="46" name="canonical_home_team_name"/>
+    <tableColumn id="47" name="original_home_team"/>
+    <tableColumn id="48" name="banned_team_id"/>
+    <tableColumn id="49" name="banned_team_name"/>
+    <tableColumn id="50" name="model_origin"/>
+    <tableColumn id="51" name="baseline_identifier"/>
+    <tableColumn id="52" name="model_state_at_decision"/>
+    <tableColumn id="53" name="model_artifact_hash"/>
+    <tableColumn id="54" name="calibration_method"/>
+    <tableColumn id="55" name="calibration_version"/>
+    <tableColumn id="56" name="calibration_artifact_hash"/>
+    <tableColumn id="57" name="feature_schema_version"/>
+    <tableColumn id="58" name="entity_map_version"/>
+    <tableColumn id="59" name="code_revision"/>
+    <tableColumn id="60" name="observed_at_utc"/>
+    <tableColumn id="61" name="correlation_tags"/>
+    <tableColumn id="62" name="decision_line"/>
+    <tableColumn id="63" name="decision_american_odds"/>
+    <tableColumn id="64" name="decision_decimal_odds"/>
+    <tableColumn id="65" name="decision_raw_implied_probability"/>
+    <tableColumn id="66" name="decision_no_vig_probability"/>
+    <tableColumn id="67" name="decision_consensus_probability"/>
+    <tableColumn id="68" name="decision_consensus_line"/>
+    <tableColumn id="69" name="closing_decimal_odds"/>
+    <tableColumn id="70" name="closing_raw_implied_probability"/>
+    <tableColumn id="71" name="closing_no_vig_probability"/>
+    <tableColumn id="72" name="closing_consensus_probability"/>
+    <tableColumn id="73" name="closing_consensus_line"/>
+    <tableColumn id="74" name="legacy_units"/>
+    <tableColumn id="75" name="void_reason"/>
+    <tableColumn id="76" name="research_score_units"/>
+    <tableColumn id="77" name="research_pnl_units"/>
+    <tableColumn id="78" name="research_scored_at_utc"/>
+    <tableColumn id="79" name="research_scoring_note"/>
+    <tableColumn id="80" name="migrated_from_version"/>
+    <tableColumn id="81" name="elo_probability"/>
+    <tableColumn id="82" name="trend_gap"/>
+    <tableColumn id="83" name="park_factor"/>
+    <tableColumn id="84" name="weather_factor"/>
+    <tableColumn id="85" name="pitcher_era_gap"/>
+    <tableColumn id="86" name="probable_starter_era_gap"/>
+    <tableColumn id="87" name="unavailable_features"/>
+    <tableColumn id="88" name="defensive_trend_gap"/>
+    <tableColumn id="89" name="neutral_elo_rating_difference"/>
+    <tableColumn id="90" name="bullpen_weakness_gap"/>
+    <tableColumn id="91" name="starter_era_gap"/>
+    <tableColumn id="92" name="rest_disparity"/>
+    <tableColumn id="93" name="back_to_back_gap"/>
+    <tableColumn id="94" name="games_last_7_gap"/>
+    <tableColumn id="95" name="schedule_missingness"/>
+    <tableColumn id="96" name="market_residual_probability"/>
+    <tableColumn id="97" name="trade_candidate"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -625,19 +756,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$2)</f>
+        <f>COUNTA('Picks'!$A$2:$A$3)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -665,19 +796,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$2,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$3,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")/(COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"win")+COUNTIFS('Picks'!$BX$2:$BX$2,"&gt;0",'Picks'!$V$2:$V$2,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")/(COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"win")+COUNTIFS('Picks'!$BX$2:$BX$3,"&gt;0",'Picks'!$V$2:$V$3,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$2)/SUM('Picks'!$BX$2:$BX$2),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$3)/SUM('Picks'!$BX$2:$BX$3),0)</f>
         <v/>
       </c>
     </row>
@@ -705,19 +836,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$2)</f>
+        <f>SUM('Picks'!$BY$2:$BY$3)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$2,"&lt;&gt;",'Picks'!$AB$2:$AB$2),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$3,"&lt;&gt;",'Picks'!$AB$2:$AB$3),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$2,'Picks'!$AM$2:$AM$2,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$3,'Picks'!$AM$2:$AM$3,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -772,15 +903,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -788,11 +919,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A14,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A14,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -803,15 +934,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -819,11 +950,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A15,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A15,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -834,15 +965,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled",'Picks'!$V$2:$V$2,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled",'Picks'!$V$2:$V$3,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -850,11 +981,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$2,'Picks'!$H$2:$H$2,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$3,'Picks'!$H$2:$H$3,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$2,'Picks'!$H$2:$H$2,$A16,'Picks'!$U$2:$U$2,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$3,'Picks'!$H$2:$H$3,$A16,'Picks'!$U$2:$U$3,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -883,7 +1014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CS1"/>
+  <dimension ref="A1:CS3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1472,9 +1603,573 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="36" customHeight="1">
+      <c r="A2" s="24" t="inlineStr">
+        <is>
+          <t>bf8dd5fa7c134ac0</t>
+        </is>
+      </c>
+      <c r="B2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:01:43.911021Z</t>
+        </is>
+      </c>
+      <c r="C2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D2" s="24" t="inlineStr">
+        <is>
+          <t>75283</t>
+        </is>
+      </c>
+      <c r="E2" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F2" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="G2" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="H2" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I2" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J2" s="25" t="n"/>
+      <c r="K2" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L2" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M2" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N2" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O2" s="28" t="n">
+        <v>0.5820070000000001</v>
+      </c>
+      <c r="P2" s="28" t="n"/>
+      <c r="Q2" s="28" t="n">
+        <v>0.201779</v>
+      </c>
+      <c r="R2" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S2" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U2" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V2" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W2" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="25" t="n"/>
+      <c r="Z2" s="26" t="n">
+        <v>178</v>
+      </c>
+      <c r="AA2" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB2" s="28" t="n">
+        <v>-0.020228</v>
+      </c>
+      <c r="AC2" s="30" t="n">
+        <v>2.0375</v>
+      </c>
+      <c r="AD2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T17:05:20.172404Z</t>
+        </is>
+      </c>
+      <c r="AE2" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-r6-vp-wbg-2026-08-09).</t>
+        </is>
+      </c>
+      <c r="AF2" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG2" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH2" s="24" t="n"/>
+      <c r="AI2" s="31" t="n"/>
+      <c r="AJ2" s="31" t="n"/>
+      <c r="AK2" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL2" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN2" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO2" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP2" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AQ2" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AR2" s="24" t="inlineStr">
+        <is>
+          <t>Weibo Gaming</t>
+        </is>
+      </c>
+      <c r="AS2" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AT2" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AU2" s="24" t="inlineStr">
+        <is>
+          <t>Virtus.pro</t>
+        </is>
+      </c>
+      <c r="AV2" s="24" t="n"/>
+      <c r="AW2" s="24" t="n"/>
+      <c r="AX2" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY2" s="24" t="n"/>
+      <c r="AZ2" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA2" s="24" t="inlineStr">
+        <is>
+          <t>3b81c1a225385446e6c2efcb53bbcef49ca7c03c0ccb69faec9e458b1a6f00c1</t>
+        </is>
+      </c>
+      <c r="BB2" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD2" s="24" t="inlineStr">
+        <is>
+          <t>3b81c1a225385446e6c2efcb53bbcef49ca7c03c0ccb69faec9e458b1a6f00c1</t>
+        </is>
+      </c>
+      <c r="BE2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF2" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG2" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH2" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-09T14:01:43.349448Z</t>
+        </is>
+      </c>
+      <c r="BI2" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ2" s="25" t="n"/>
+      <c r="BK2" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL2" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM2" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN2" s="28" t="n"/>
+      <c r="BO2" s="28" t="n"/>
+      <c r="BP2" s="25" t="n"/>
+      <c r="BQ2" s="27" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BR2" s="28" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BS2" s="28" t="n"/>
+      <c r="BT2" s="28" t="n"/>
+      <c r="BU2" s="25" t="n"/>
+      <c r="BV2" s="29" t="n"/>
+      <c r="BW2" s="24" t="n"/>
+      <c r="BX2" s="30" t="n"/>
+      <c r="BY2" s="27" t="n"/>
+      <c r="BZ2" s="24" t="n"/>
+      <c r="CA2" s="31" t="n"/>
+      <c r="CB2" s="24" t="n"/>
+      <c r="CC2" s="24" t="n"/>
+      <c r="CD2" s="24" t="n"/>
+      <c r="CE2" s="24" t="n"/>
+      <c r="CF2" s="24" t="n"/>
+      <c r="CG2" s="24" t="n"/>
+      <c r="CH2" s="24" t="n"/>
+      <c r="CI2" s="24" t="n"/>
+      <c r="CJ2" s="24" t="n"/>
+      <c r="CK2" s="24" t="n"/>
+      <c r="CL2" s="24" t="n"/>
+      <c r="CM2" s="24" t="n"/>
+      <c r="CN2" s="24" t="n"/>
+      <c r="CO2" s="24" t="n"/>
+      <c r="CP2" s="24" t="n"/>
+      <c r="CQ2" s="24" t="n"/>
+      <c r="CR2" s="24" t="n"/>
+      <c r="CS2" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="36" customHeight="1">
+      <c r="A3" s="24" t="inlineStr">
+        <is>
+          <t>042d0460cb5b40c6</t>
+        </is>
+      </c>
+      <c r="B3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:27.133025Z</t>
+        </is>
+      </c>
+      <c r="C3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T17:00:00Z</t>
+        </is>
+      </c>
+      <c r="D3" s="24" t="inlineStr">
+        <is>
+          <t>77480</t>
+        </is>
+      </c>
+      <c r="E3" s="24" t="inlineStr">
+        <is>
+          <t>RAINBOW_SIX</t>
+        </is>
+      </c>
+      <c r="F3" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="G3" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Clan</t>
+        </is>
+      </c>
+      <c r="H3" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I3" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L3" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M3" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N3" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O3" s="28" t="n">
+        <v>0.739148</v>
+      </c>
+      <c r="P3" s="28" t="n"/>
+      <c r="Q3" s="28" t="n">
+        <v>0.119376</v>
+      </c>
+      <c r="R3" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S3" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U3" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="n"/>
+      <c r="W3" s="26" t="n"/>
+      <c r="X3" s="26" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="26" t="n"/>
+      <c r="AA3" s="28" t="n"/>
+      <c r="AB3" s="28" t="n"/>
+      <c r="AC3" s="30" t="n"/>
+      <c r="AD3" s="24" t="n"/>
+      <c r="AE3" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-r6-faze-liquid-2026-08-13).</t>
+        </is>
+      </c>
+      <c r="AF3" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG3" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH3" s="24" t="n"/>
+      <c r="AI3" s="31" t="n"/>
+      <c r="AJ3" s="31" t="n"/>
+      <c r="AK3" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL3" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="AM3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN3" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO3" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP3" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AQ3" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AR3" s="24" t="inlineStr">
+        <is>
+          <t>Team Liquid</t>
+        </is>
+      </c>
+      <c r="AS3" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Clan</t>
+        </is>
+      </c>
+      <c r="AT3" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Clan</t>
+        </is>
+      </c>
+      <c r="AU3" s="24" t="inlineStr">
+        <is>
+          <t>FaZe Clan</t>
+        </is>
+      </c>
+      <c r="AV3" s="24" t="n"/>
+      <c r="AW3" s="24" t="n"/>
+      <c r="AX3" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY3" s="24" t="n"/>
+      <c r="AZ3" s="24" t="inlineStr">
+        <is>
+          <t>research</t>
+        </is>
+      </c>
+      <c r="BA3" s="24" t="inlineStr">
+        <is>
+          <t>2dfefd2258c1f6dfaf21ec195dd0ad9f26d9b256b7c7b984568fe75dbc5e12d4</t>
+        </is>
+      </c>
+      <c r="BB3" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD3" s="24" t="inlineStr">
+        <is>
+          <t>2dfefd2258c1f6dfaf21ec195dd0ad9f26d9b256b7c7b984568fe75dbc5e12d4</t>
+        </is>
+      </c>
+      <c r="BE3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF3" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG3" s="24" t="inlineStr">
+        <is>
+          <t>rainbow_six-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-12T17:44:27.132333Z</t>
+        </is>
+      </c>
+      <c r="BI3" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ3" s="25" t="n"/>
+      <c r="BK3" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL3" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM3" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN3" s="28" t="n"/>
+      <c r="BO3" s="28" t="n"/>
+      <c r="BP3" s="25" t="n"/>
+      <c r="BQ3" s="27" t="n"/>
+      <c r="BR3" s="28" t="n"/>
+      <c r="BS3" s="28" t="n"/>
+      <c r="BT3" s="28" t="n"/>
+      <c r="BU3" s="25" t="n"/>
+      <c r="BV3" s="29" t="n"/>
+      <c r="BW3" s="24" t="n"/>
+      <c r="BX3" s="30" t="n"/>
+      <c r="BY3" s="27" t="n"/>
+      <c r="BZ3" s="24" t="n"/>
+      <c r="CA3" s="31" t="n"/>
+      <c r="CB3" s="24" t="n"/>
+      <c r="CC3" s="24" t="n"/>
+      <c r="CD3" s="24" t="n"/>
+      <c r="CE3" s="24" t="n"/>
+      <c r="CF3" s="24" t="n"/>
+      <c r="CG3" s="24" t="n"/>
+      <c r="CH3" s="24" t="n"/>
+      <c r="CI3" s="24" t="n"/>
+      <c r="CJ3" s="24" t="n"/>
+      <c r="CK3" s="24" t="n"/>
+      <c r="CL3" s="24" t="n"/>
+      <c r="CM3" s="24" t="n"/>
+      <c r="CN3" s="24" t="n"/>
+      <c r="CO3" s="24" t="n"/>
+      <c r="CP3" s="24" t="n"/>
+      <c r="CQ3" s="24" t="n"/>
+      <c r="CR3" s="24" t="n"/>
+      <c r="CS3" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:CS1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/data/gated_research/rainbow_six.xlsx
+++ b/data/gated_research/rainbow_six.xlsx
@@ -1899,22 +1899,22 @@
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="24" t="inlineStr">
         <is>
-          <t>042d0460cb5b40c6</t>
+          <t>3ea18b4364c845ca</t>
         </is>
       </c>
       <c r="B3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:27.133025Z</t>
+          <t>2026-08-13T13:47:13.395027Z</t>
         </is>
       </c>
       <c r="C3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-13T17:00:00Z</t>
+          <t>2026-08-13T14:00:00Z</t>
         </is>
       </c>
       <c r="D3" s="24" t="inlineStr">
         <is>
-          <t>77480</t>
+          <t>77319</t>
         </is>
       </c>
       <c r="E3" s="24" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="F3" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="G3" s="24" t="inlineStr">
         <is>
-          <t>FaZe Clan</t>
+          <t>Geekay Esports</t>
         </is>
       </c>
       <c r="H3" s="24" t="inlineStr">
@@ -1949,26 +1949,26 @@
         </is>
       </c>
       <c r="L3" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="M3" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="N3" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="O3" s="28" t="n">
-        <v>0.739148</v>
+        <v>0.642788</v>
       </c>
       <c r="P3" s="28" t="n"/>
       <c r="Q3" s="28" t="n">
-        <v>0.119376</v>
+        <v>0.033413</v>
       </c>
       <c r="R3" s="26" t="n">
-        <v>80</v>
+        <v>37</v>
       </c>
       <c r="S3" s="29" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="T3" s="24" t="inlineStr">
         <is>
@@ -1977,21 +1977,41 @@
       </c>
       <c r="U3" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V3" s="24" t="n"/>
-      <c r="W3" s="26" t="n"/>
-      <c r="X3" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V3" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W3" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="26" t="n"/>
-      <c r="AA3" s="28" t="n"/>
-      <c r="AB3" s="28" t="n"/>
-      <c r="AC3" s="30" t="n"/>
-      <c r="AD3" s="24" t="n"/>
+      <c r="Z3" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA3" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.000625</v>
+      </c>
+      <c r="AC3" s="30" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="AD3" s="24" t="inlineStr">
+        <is>
+          <t>2026-08-13T16:50:25.715804Z</t>
+        </is>
+      </c>
       <c r="AE3" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6200 (market_slug=aec-r6-faze-liquid-2026-08-13).</t>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-r6-ge-secret-2026-08-13).</t>
         </is>
       </c>
       <c r="AF3" s="31" t="inlineStr">
@@ -2032,32 +2052,32 @@
       </c>
       <c r="AP3" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AQ3" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AR3" s="24" t="inlineStr">
         <is>
-          <t>Team Liquid</t>
+          <t>Team Secret</t>
         </is>
       </c>
       <c r="AS3" s="24" t="inlineStr">
         <is>
-          <t>FaZe Clan</t>
+          <t>Geekay Esports</t>
         </is>
       </c>
       <c r="AT3" s="24" t="inlineStr">
         <is>
-          <t>FaZe Clan</t>
+          <t>Geekay Esports</t>
         </is>
       </c>
       <c r="AU3" s="24" t="inlineStr">
         <is>
-          <t>FaZe Clan</t>
+          <t>Geekay Esports</t>
         </is>
       </c>
       <c r="AV3" s="24" t="n"/>
@@ -2075,7 +2095,7 @@
       </c>
       <c r="BA3" s="24" t="inlineStr">
         <is>
-          <t>2dfefd2258c1f6dfaf21ec195dd0ad9f26d9b256b7c7b984568fe75dbc5e12d4</t>
+          <t>5abfbacc5cb76b78275a1604ae93eb223c0b4a7794a63b0d764f8921f60f0e7b</t>
         </is>
       </c>
       <c r="BB3" s="24" t="inlineStr">
@@ -2090,7 +2110,7 @@
       </c>
       <c r="BD3" s="24" t="inlineStr">
         <is>
-          <t>2dfefd2258c1f6dfaf21ec195dd0ad9f26d9b256b7c7b984568fe75dbc5e12d4</t>
+          <t>5abfbacc5cb76b78275a1604ae93eb223c0b4a7794a63b0d764f8921f60f0e7b</t>
         </is>
       </c>
       <c r="BE3" s="24" t="inlineStr">
@@ -2110,7 +2130,7 @@
       </c>
       <c r="BH3" s="24" t="inlineStr">
         <is>
-          <t>2026-08-12T17:44:27.132333Z</t>
+          <t>2026-08-13T13:47:12.403984Z</t>
         </is>
       </c>
       <c r="BI3" s="24" t="inlineStr">
@@ -2120,19 +2140,23 @@
       </c>
       <c r="BJ3" s="25" t="n"/>
       <c r="BK3" s="26" t="n">
-        <v>-163</v>
+        <v>-156</v>
       </c>
       <c r="BL3" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.641026</v>
       </c>
       <c r="BM3" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.609375</v>
       </c>
       <c r="BN3" s="28" t="n"/>
       <c r="BO3" s="28" t="n"/>
       <c r="BP3" s="25" t="n"/>
-      <c r="BQ3" s="27" t="n"/>
-      <c r="BR3" s="28" t="n"/>
+      <c r="BQ3" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR3" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS3" s="28" t="n"/>
       <c r="BT3" s="28" t="n"/>
       <c r="BU3" s="25" t="n"/>
